--- a/output/turnaround_watch.xlsx
+++ b/output/turnaround_watch.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,100 +429,115 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>cash_from_operations_cr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>roce_percentage</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>market_cap_crore</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>opm_percentage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>broad_sector</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dividend_payout_ratio_pct</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
         <is>
           <t>composite_quality_score</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>roce_percentage</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>market_cap_crore</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>opm_percentage</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>broad_sector</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>dividend_payout_ratio_pct</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>sector_relative_score</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>revenue_cagr_3yr</t>
         </is>
@@ -531,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,68 +555,81 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48.28</v>
+        <v>882</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>26.02</v>
       </c>
       <c r="E2" t="n">
-        <v>8.300000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.55</v>
+        <v>0.02</v>
       </c>
       <c r="G2" t="n">
-        <v>17651</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>667</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.96</v>
+      </c>
       <c r="K2" t="n">
-        <v>88.79000000000001</v>
+        <v>29.17</v>
       </c>
       <c r="L2" t="n">
-        <v>32.2</v>
+        <v>28.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1372183.55</v>
+        <v>53.8</v>
       </c>
       <c r="N2" t="n">
-        <v>44.57</v>
+        <v>1258520.29</v>
       </c>
       <c r="O2" t="n">
-        <v>9.91</v>
+        <v>60.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>5.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>50351</v>
+        <v>1.08</v>
       </c>
       <c r="R2" t="n">
-        <v>20829</v>
+        <v>4270</v>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
+        <v>1111</v>
+      </c>
+      <c r="T2" t="n">
+        <v>34</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V2" t="n">
-        <v>24.29479715622616</v>
+        <v>47</v>
+      </c>
+      <c r="W2" t="n">
+        <v>74.0978734217103</v>
+      </c>
+      <c r="X2" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>76.46921430165466</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,72 +638,81 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.15</v>
+        <v>4175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.59</v>
+        <v>16.12</v>
       </c>
       <c r="E3" t="n">
-        <v>9.93</v>
+        <v>117.75</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74</v>
+        <v>0.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3106</v>
+        <v>41.19</v>
       </c>
       <c r="H3" t="n">
-        <v>6.93</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>30.59</v>
+        <v>2938</v>
       </c>
       <c r="J3" t="n">
-        <v>30.39</v>
+        <v>14.55</v>
       </c>
       <c r="K3" t="n">
-        <v>88.79000000000001</v>
+        <v>14.85</v>
       </c>
       <c r="L3" t="n">
-        <v>23.2</v>
+        <v>15.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1870170.39</v>
+        <v>185.43</v>
       </c>
       <c r="N3" t="n">
-        <v>46.4</v>
+        <v>1677775.19</v>
       </c>
       <c r="O3" t="n">
-        <v>6.43</v>
+        <v>54.96</v>
       </c>
       <c r="P3" t="n">
-        <v>1.22</v>
+        <v>14.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>10728</v>
+        <v>3.85</v>
       </c>
       <c r="R3" t="n">
-        <v>1656</v>
+        <v>24394</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>57</v>
+        <v>3933</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
       </c>
       <c r="V3" t="n">
-        <v>10.25183069859263</v>
+        <v>79</v>
+      </c>
+      <c r="W3" t="n">
+        <v>67.99817496750697</v>
+      </c>
+      <c r="X3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18.28200866249903</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -684,72 +721,77 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.47</v>
+        <v>14170</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>41.37</v>
       </c>
       <c r="E4" t="n">
-        <v>141.75</v>
+        <v>48.28</v>
       </c>
       <c r="F4" t="n">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>797</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>9.720000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="I4" t="n">
-        <v>21.69</v>
+        <v>17651</v>
       </c>
       <c r="J4" t="n">
-        <v>21.66</v>
-      </c>
-      <c r="K4" t="n">
-        <v>86.56</v>
-      </c>
-      <c r="L4" t="n">
-        <v>46</v>
-      </c>
+        <v>16.09</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1536236.24</v>
+        <v>32.2</v>
       </c>
       <c r="N4" t="n">
-        <v>75.58</v>
+        <v>1372183.55</v>
       </c>
       <c r="O4" t="n">
-        <v>4.48</v>
+        <v>44.57</v>
       </c>
       <c r="P4" t="n">
-        <v>0.96</v>
+        <v>9.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>5849</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
-        <v>1201</v>
+        <v>50351</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>73</v>
+        <v>20829</v>
+      </c>
+      <c r="T4" t="n">
+        <v>36</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V4" t="n">
-        <v>10.71372178938566</v>
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>65.88004576104804</v>
+      </c>
+      <c r="X4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>24.29479715622616</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -758,72 +800,81 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.09</v>
+        <v>1349</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>11.94</v>
       </c>
       <c r="E5" t="n">
-        <v>58.33</v>
+        <v>36.31</v>
       </c>
       <c r="F5" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="G5" t="n">
-        <v>11372</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>10.78</v>
+        <v>1.73</v>
       </c>
       <c r="I5" t="n">
-        <v>24.54</v>
+        <v>841</v>
       </c>
       <c r="J5" t="n">
-        <v>29.46</v>
+        <v>36.31</v>
       </c>
       <c r="K5" t="n">
-        <v>85.44</v>
+        <v>73.11</v>
       </c>
       <c r="L5" t="n">
-        <v>17.3</v>
+        <v>69.52</v>
       </c>
       <c r="M5" t="n">
-        <v>1339586.09</v>
+        <v>23.8</v>
       </c>
       <c r="N5" t="n">
-        <v>37.9</v>
+        <v>571322.04</v>
       </c>
       <c r="O5" t="n">
-        <v>6.71</v>
+        <v>8.65</v>
       </c>
       <c r="P5" t="n">
-        <v>3.88</v>
+        <v>11.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>48497</v>
+        <v>3.46</v>
       </c>
       <c r="R5" t="n">
-        <v>9610</v>
+        <v>12375</v>
       </c>
       <c r="S5" t="n">
-        <v>28</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>34</v>
+        <v>1477</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V5" t="n">
-        <v>13.12675558948349</v>
+        <v>8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>65.57351320201516</v>
+      </c>
+      <c r="X5" t="n">
+        <v>78.61076524612234</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>68.36335197744833</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -832,66 +883,75 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>117.75</v>
+        <v>1213</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
+        <v>20.53</v>
       </c>
       <c r="E6" t="n">
-        <v>41.19</v>
+        <v>32.47</v>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>0.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2938</v>
+        <v>141.75</v>
       </c>
       <c r="H6" t="n">
-        <v>14.55</v>
+        <v>1.13</v>
       </c>
       <c r="I6" t="n">
-        <v>14.85</v>
+        <v>797</v>
       </c>
       <c r="J6" t="n">
-        <v>15.44</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>84.19</v>
+        <v>21.69</v>
       </c>
       <c r="L6" t="n">
-        <v>185.43</v>
+        <v>21.66</v>
       </c>
       <c r="M6" t="n">
-        <v>1677775.19</v>
+        <v>46</v>
       </c>
       <c r="N6" t="n">
-        <v>54.96</v>
+        <v>1536236.24</v>
       </c>
       <c r="O6" t="n">
-        <v>14.34</v>
+        <v>75.58</v>
       </c>
       <c r="P6" t="n">
-        <v>3.85</v>
+        <v>4.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>24394</v>
+        <v>0.96</v>
       </c>
       <c r="R6" t="n">
-        <v>3933</v>
+        <v>5849</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>79</v>
+        <v>1201</v>
+      </c>
+      <c r="T6" t="n">
+        <v>25</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
       </c>
       <c r="V6" t="n">
-        <v>18.28200866249903</v>
+        <v>73</v>
+      </c>
+      <c r="W6" t="n">
+        <v>65.34431240069731</v>
+      </c>
+      <c r="X6" t="n">
+        <v>83.65918984617954</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>10.71372178938566</v>
       </c>
     </row>
     <row r="7">
@@ -906,72 +966,81 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>25210</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="E7" t="n">
         <v>29.79</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>0.09</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>87.52</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1.13</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>20117</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>11.24</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>12.47</v>
       </c>
-      <c r="K7" t="n">
-        <v>83.59</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>40</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>35.99</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>4.1</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>153670</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>26248</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>24</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
+        <v>60.72864355840955</v>
+      </c>
+      <c r="X7" t="n">
+        <v>85.04353517246395</v>
+      </c>
+      <c r="Y7" t="n">
         <v>15.21650079880636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -980,72 +1049,81 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34.4</v>
+        <v>35936</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02</v>
+        <v>5.99</v>
       </c>
       <c r="E8" t="n">
-        <v>82.73999999999999</v>
+        <v>35.51</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="G8" t="n">
-        <v>667</v>
+        <v>11.36</v>
       </c>
       <c r="H8" t="n">
-        <v>17.96</v>
+        <v>2.21</v>
       </c>
       <c r="I8" t="n">
-        <v>29.17</v>
+        <v>25415</v>
       </c>
       <c r="J8" t="n">
-        <v>28.47</v>
+        <v>8.48</v>
       </c>
       <c r="K8" t="n">
-        <v>83.34</v>
+        <v>25.79</v>
       </c>
       <c r="L8" t="n">
-        <v>53.8</v>
+        <v>28.06</v>
       </c>
       <c r="M8" t="n">
-        <v>1258520.29</v>
+        <v>32.1</v>
       </c>
       <c r="N8" t="n">
-        <v>60.44</v>
+        <v>468662.13</v>
       </c>
       <c r="O8" t="n">
-        <v>5.74</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>0.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>4270</v>
+        <v>1.15</v>
       </c>
       <c r="R8" t="n">
-        <v>1111</v>
+        <v>448083</v>
       </c>
       <c r="S8" t="n">
-        <v>34</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>47</v>
+        <v>26859</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V8" t="n">
-        <v>76.46921430165466</v>
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>54.03514462999922</v>
+      </c>
+      <c r="X8" t="n">
+        <v>66.44562239340382</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>24.86362936813233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1054,72 +1132,81 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36.31</v>
+        <v>15018</v>
       </c>
       <c r="D9" t="n">
-        <v>0.43</v>
+        <v>30.34</v>
       </c>
       <c r="E9" t="n">
-        <v>8.039999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>841</v>
+        <v>5.95</v>
       </c>
       <c r="H9" t="n">
-        <v>36.31</v>
+        <v>0.23</v>
       </c>
       <c r="I9" t="n">
-        <v>73.11</v>
+        <v>8250</v>
       </c>
       <c r="J9" t="n">
-        <v>69.52</v>
+        <v>19.58</v>
       </c>
       <c r="K9" t="n">
-        <v>80.95</v>
+        <v>14.91</v>
       </c>
       <c r="L9" t="n">
-        <v>23.8</v>
+        <v>14.87</v>
       </c>
       <c r="M9" t="n">
-        <v>571322.04</v>
+        <v>12.9</v>
       </c>
       <c r="N9" t="n">
-        <v>8.65</v>
+        <v>675598.01</v>
       </c>
       <c r="O9" t="n">
-        <v>11.82</v>
+        <v>48.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.46</v>
+        <v>2.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>12375</v>
+        <v>1.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1477</v>
+        <v>26711</v>
       </c>
       <c r="S9" t="n">
+        <v>8104</v>
+      </c>
+      <c r="T9" t="n">
+        <v>58</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
         <v>16</v>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>68.36335197744833</v>
+      <c r="W9" t="n">
+        <v>53.85496094664723</v>
+      </c>
+      <c r="X9" t="n">
+        <v>61.50582955610891</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>28.63193631184944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1128,72 +1215,81 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.35</v>
+        <v>3266</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9399999999999999</v>
+        <v>15.44</v>
       </c>
       <c r="E10" t="n">
-        <v>5.95</v>
+        <v>24.15</v>
       </c>
       <c r="F10" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="G10" t="n">
-        <v>8250</v>
+        <v>9.93</v>
       </c>
       <c r="H10" t="n">
-        <v>19.58</v>
+        <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>14.91</v>
+        <v>3106</v>
       </c>
       <c r="J10" t="n">
-        <v>14.87</v>
+        <v>6.93</v>
       </c>
       <c r="K10" t="n">
-        <v>77.59</v>
+        <v>30.59</v>
       </c>
       <c r="L10" t="n">
-        <v>12.9</v>
+        <v>30.39</v>
       </c>
       <c r="M10" t="n">
-        <v>675598.01</v>
+        <v>23.2</v>
       </c>
       <c r="N10" t="n">
-        <v>48.9</v>
+        <v>1870170.39</v>
       </c>
       <c r="O10" t="n">
-        <v>2.31</v>
+        <v>46.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.16</v>
+        <v>6.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>26711</v>
+        <v>1.22</v>
       </c>
       <c r="R10" t="n">
-        <v>8104</v>
+        <v>10728</v>
       </c>
       <c r="S10" t="n">
-        <v>58</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>16</v>
+        <v>1656</v>
+      </c>
+      <c r="T10" t="n">
+        <v>31</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
       </c>
       <c r="V10" t="n">
-        <v>28.63193631184944</v>
+        <v>57</v>
+      </c>
+      <c r="W10" t="n">
+        <v>51.43629651769113</v>
+      </c>
+      <c r="X10" t="n">
+        <v>49.66542051496325</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10.25183069859263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1202,72 +1298,81 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35.51</v>
+        <v>2746</v>
       </c>
       <c r="D11" t="n">
-        <v>0.72</v>
+        <v>4.99</v>
       </c>
       <c r="E11" t="n">
-        <v>11.36</v>
+        <v>13.56</v>
       </c>
       <c r="F11" t="n">
-        <v>2.21</v>
+        <v>0.03</v>
       </c>
       <c r="G11" t="n">
-        <v>25415</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>8.48</v>
+        <v>2.4</v>
       </c>
       <c r="I11" t="n">
-        <v>25.79</v>
+        <v>278</v>
       </c>
       <c r="J11" t="n">
-        <v>28.06</v>
+        <v>20.48</v>
       </c>
       <c r="K11" t="n">
-        <v>76.27</v>
+        <v>22.97</v>
       </c>
       <c r="L11" t="n">
-        <v>32.1</v>
+        <v>22.74</v>
       </c>
       <c r="M11" t="n">
-        <v>468662.13</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>68.15000000000001</v>
+        <v>3053088.97</v>
       </c>
       <c r="O11" t="n">
-        <v>0.72</v>
+        <v>72.53</v>
       </c>
       <c r="P11" t="n">
-        <v>1.15</v>
+        <v>11.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>448083</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>26859</v>
+        <v>50789</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>33</v>
+        <v>2536</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V11" t="n">
-        <v>24.86362936813233</v>
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>51.2431631105219</v>
+      </c>
+      <c r="X11" t="n">
+        <v>42.65320194371608</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>28.1325519519273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1276,72 +1381,81 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.55</v>
+        <v>12135</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>19.82</v>
       </c>
       <c r="E12" t="n">
-        <v>35.34</v>
+        <v>15.09</v>
       </c>
       <c r="F12" t="n">
-        <v>0.79</v>
+        <v>0.05</v>
       </c>
       <c r="G12" t="n">
-        <v>1152</v>
+        <v>58.33</v>
       </c>
       <c r="H12" t="n">
-        <v>9.51</v>
+        <v>0.57</v>
       </c>
       <c r="I12" t="n">
-        <v>22.73</v>
+        <v>11372</v>
       </c>
       <c r="J12" t="n">
-        <v>21.83</v>
+        <v>10.78</v>
       </c>
       <c r="K12" t="n">
-        <v>75.34</v>
+        <v>24.54</v>
       </c>
       <c r="L12" t="n">
-        <v>22.8</v>
+        <v>29.46</v>
       </c>
       <c r="M12" t="n">
-        <v>439803.15</v>
+        <v>17.3</v>
       </c>
       <c r="N12" t="n">
-        <v>59.75</v>
+        <v>1339586.09</v>
       </c>
       <c r="O12" t="n">
-        <v>5.93</v>
+        <v>37.9</v>
       </c>
       <c r="P12" t="n">
-        <v>0.12</v>
+        <v>6.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>25774</v>
+        <v>3.88</v>
       </c>
       <c r="R12" t="n">
-        <v>4154</v>
+        <v>48497</v>
       </c>
       <c r="S12" t="n">
-        <v>6291</v>
-      </c>
-      <c r="T12" t="inlineStr">
+        <v>9610</v>
+      </c>
+      <c r="T12" t="n">
+        <v>28</v>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="U12" t="n">
-        <v>25</v>
-      </c>
       <c r="V12" t="n">
-        <v>10.38975593522793</v>
+        <v>34</v>
+      </c>
+      <c r="W12" t="n">
+        <v>50.96536737685161</v>
+      </c>
+      <c r="X12" t="n">
+        <v>44.6485862749794</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.12675558948349</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1350,72 +1464,81 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.369999999999999</v>
+        <v>4134</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08</v>
+        <v>16.12</v>
       </c>
       <c r="E13" t="n">
-        <v>19.83</v>
+        <v>15.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.73</v>
+        <v>0.02</v>
       </c>
       <c r="G13" t="n">
-        <v>1929</v>
+        <v>35.34</v>
       </c>
       <c r="H13" t="n">
-        <v>10.33</v>
+        <v>0.79</v>
       </c>
       <c r="I13" t="n">
-        <v>11.29</v>
+        <v>1152</v>
       </c>
       <c r="J13" t="n">
-        <v>10.68</v>
+        <v>9.51</v>
       </c>
       <c r="K13" t="n">
-        <v>71.61</v>
+        <v>22.73</v>
       </c>
       <c r="L13" t="n">
-        <v>14.8</v>
+        <v>21.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3154358.33</v>
+        <v>22.8</v>
       </c>
       <c r="N13" t="n">
-        <v>25.87</v>
+        <v>439803.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>59.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>5.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>20521</v>
+        <v>0.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1733</v>
+        <v>25774</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U13" t="n">
-        <v>16</v>
+        <v>4154</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6291</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
       </c>
       <c r="V13" t="n">
-        <v>14.80997180241832</v>
+        <v>25</v>
+      </c>
+      <c r="W13" t="n">
+        <v>49.41254914926012</v>
+      </c>
+      <c r="X13" t="n">
+        <v>28.10632762697017</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10.38975593522793</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1424,72 +1547,81 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.53</v>
+        <v>157284</v>
       </c>
       <c r="D14" t="n">
-        <v>0.72</v>
+        <v>28.89</v>
       </c>
       <c r="E14" t="n">
-        <v>10.28</v>
+        <v>17.99</v>
       </c>
       <c r="F14" t="n">
-        <v>1.61</v>
+        <v>6.45</v>
       </c>
       <c r="G14" t="n">
-        <v>39635</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>8.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>20.1</v>
+        <v>12547</v>
       </c>
       <c r="J14" t="n">
-        <v>20.11</v>
+        <v>17.25</v>
       </c>
       <c r="K14" t="n">
-        <v>71.18000000000001</v>
+        <v>51.95</v>
       </c>
       <c r="L14" t="n">
-        <v>21.31</v>
+        <v>55.18</v>
       </c>
       <c r="M14" t="n">
-        <v>1418164.33</v>
+        <v>7.6</v>
       </c>
       <c r="N14" t="n">
-        <v>28.61</v>
+        <v>1319221.86</v>
       </c>
       <c r="O14" t="n">
-        <v>4.24</v>
+        <v>25.76</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>6.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>776352</v>
+        <v>3.43</v>
       </c>
       <c r="R14" t="n">
-        <v>43161</v>
+        <v>159516</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>40</v>
+        <v>46081</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-14152</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V14" t="n">
-        <v>28.72779122527918</v>
+        <v>16</v>
+      </c>
+      <c r="W14" t="n">
+        <v>48.83992353907501</v>
+      </c>
+      <c r="X14" t="n">
+        <v>42.47098526296872</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21.39660074377121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1498,72 +1630,83 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.94</v>
+        <v>16801</v>
       </c>
       <c r="D15" t="n">
-        <v>0.45</v>
+        <v>9.51</v>
       </c>
       <c r="E15" t="n">
-        <v>11.36</v>
+        <v>15.75</v>
       </c>
       <c r="F15" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G15" t="n">
-        <v>42060</v>
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>10.97</v>
+        <v>4936</v>
       </c>
       <c r="J15" t="n">
-        <v>10.2</v>
+        <v>10.51</v>
       </c>
       <c r="K15" t="n">
-        <v>70.45999999999999</v>
+        <v>12.01</v>
       </c>
       <c r="L15" t="n">
-        <v>19.71</v>
+        <v>11.14</v>
       </c>
       <c r="M15" t="n">
-        <v>390111.05</v>
+        <v>23.67</v>
       </c>
       <c r="N15" t="n">
-        <v>18.15</v>
+        <v>1503863.63</v>
       </c>
       <c r="O15" t="n">
-        <v>10.36</v>
+        <v>20.78</v>
       </c>
       <c r="P15" t="n">
-        <v>1.11</v>
+        <v>8.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>591396</v>
+        <v>1.78</v>
       </c>
       <c r="R15" t="n">
-        <v>57101</v>
+        <v>141858</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U15" t="n">
-        <v>31</v>
+        <v>13488</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
       </c>
       <c r="V15" t="n">
-        <v>24.85526395727469</v>
+        <v>29</v>
+      </c>
+      <c r="W15" t="n">
+        <v>46.94201315314325</v>
+      </c>
+      <c r="X15" t="n">
+        <v>31.86080183638076</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>26.32364432616601</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1572,72 +1715,81 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.57</v>
+        <v>71099</v>
       </c>
       <c r="D16" t="n">
-        <v>0.53</v>
+        <v>5.56</v>
       </c>
       <c r="E16" t="n">
-        <v>126.47</v>
+        <v>23.53</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="G16" t="n">
-        <v>9789</v>
+        <v>10.28</v>
       </c>
       <c r="H16" t="n">
-        <v>10.59</v>
+        <v>1.61</v>
       </c>
       <c r="I16" t="n">
-        <v>13.07</v>
+        <v>39635</v>
       </c>
       <c r="J16" t="n">
-        <v>13.4</v>
+        <v>8.01</v>
       </c>
       <c r="K16" t="n">
-        <v>69.38</v>
+        <v>20.1</v>
       </c>
       <c r="L16" t="n">
-        <v>11.3</v>
+        <v>20.11</v>
       </c>
       <c r="M16" t="n">
-        <v>722281.1</v>
+        <v>21.31</v>
       </c>
       <c r="N16" t="n">
-        <v>56.45</v>
+        <v>1418164.33</v>
       </c>
       <c r="O16" t="n">
-        <v>9.32</v>
+        <v>28.61</v>
       </c>
       <c r="P16" t="n">
-        <v>0.98</v>
+        <v>4.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>215962</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
-        <v>10155</v>
+        <v>776352</v>
       </c>
       <c r="S16" t="n">
-        <v>23872</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>8</v>
+        <v>43161</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V16" t="n">
-        <v>17.83085522343517</v>
+        <v>40</v>
+      </c>
+      <c r="W16" t="n">
+        <v>44.26096590356018</v>
+      </c>
+      <c r="X16" t="n">
+        <v>38.75721198349318</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>28.72779122527918</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1646,72 +1798,81 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13.27</v>
+        <v>19069</v>
       </c>
       <c r="D17" t="n">
-        <v>1.48</v>
+        <v>23.07</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6</v>
+        <v>14.34</v>
       </c>
       <c r="F17" t="n">
-        <v>0.37</v>
+        <v>6.81</v>
       </c>
       <c r="G17" t="n">
-        <v>8644</v>
+        <v>1.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>8.74</v>
+        <v>35669</v>
       </c>
       <c r="J17" t="n">
-        <v>8.449999999999999</v>
+        <v>21.95</v>
       </c>
       <c r="K17" t="n">
-        <v>68.90000000000001</v>
+        <v>23.87</v>
       </c>
       <c r="L17" t="n">
-        <v>10.58</v>
+        <v>15.42</v>
       </c>
       <c r="M17" t="n">
-        <v>907823.11</v>
+        <v>7.67</v>
       </c>
       <c r="N17" t="n">
-        <v>30.8</v>
+        <v>808359.03</v>
       </c>
       <c r="O17" t="n">
-        <v>5.24</v>
+        <v>49.42</v>
       </c>
       <c r="P17" t="n">
-        <v>0.06</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>178501</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>21332</v>
+        <v>283649</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
-        <v>36</v>
+        <v>65446</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-44685</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V17" t="n">
-        <v>16.97193810203161</v>
+        <v>23</v>
+      </c>
+      <c r="W17" t="n">
+        <v>44.08554497818926</v>
+      </c>
+      <c r="X17" t="n">
+        <v>29.13661940852842</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>30.18695614094877</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1720,74 +1881,77 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.75</v>
+        <v>67915</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>7.26</v>
+      </c>
+      <c r="E18" t="n">
+        <v>37.46</v>
       </c>
       <c r="F18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>4936</v>
+        <v>6.53</v>
       </c>
       <c r="H18" t="n">
-        <v>10.51</v>
+        <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>12.01</v>
+        <v>45133</v>
       </c>
       <c r="J18" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="L18" t="n">
-        <v>23.67</v>
-      </c>
+        <v>7.72</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>1503863.63</v>
+        <v>20.1</v>
       </c>
       <c r="N18" t="n">
-        <v>20.78</v>
+        <v>1504106.64</v>
       </c>
       <c r="O18" t="n">
-        <v>8.26</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>0.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>141858</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>13488</v>
+        <v>437928</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="inlineStr">
+        <v>31807</v>
+      </c>
+      <c r="T18" t="n">
+        <v>14</v>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="U18" t="n">
-        <v>29</v>
-      </c>
       <c r="V18" t="n">
-        <v>26.32364432616601</v>
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>43.15698106698831</v>
+      </c>
+      <c r="X18" t="n">
+        <v>22.36343924784591</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>20.57936456937097</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1796,72 +1960,81 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.960000000000001</v>
+        <v>15046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.58</v>
+        <v>13.94</v>
       </c>
       <c r="E19" t="n">
-        <v>7.73</v>
+        <v>16.72</v>
       </c>
       <c r="F19" t="n">
-        <v>0.51</v>
+        <v>14.87</v>
       </c>
       <c r="G19" t="n">
-        <v>45207</v>
+        <v>1.61</v>
       </c>
       <c r="H19" t="n">
-        <v>9.609999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>14.68</v>
+        <v>13296</v>
       </c>
       <c r="J19" t="n">
-        <v>11.95</v>
+        <v>18.18</v>
       </c>
       <c r="K19" t="n">
-        <v>67.22</v>
+        <v>85.78</v>
       </c>
       <c r="L19" t="n">
-        <v>9.609999999999999</v>
+        <v>53.42</v>
       </c>
       <c r="M19" t="n">
-        <v>432472.71</v>
+        <v>6.63</v>
       </c>
       <c r="N19" t="n">
-        <v>58.34</v>
+        <v>496415.88</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>36.74</v>
       </c>
       <c r="P19" t="n">
-        <v>4.21</v>
+        <v>12.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>899041</v>
+        <v>3.81</v>
       </c>
       <c r="R19" t="n">
-        <v>79020</v>
+        <v>110519</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>10</v>
+        <v>15401</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-7745</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V19" t="n">
-        <v>24.46173600944801</v>
+        <v>19</v>
+      </c>
+      <c r="W19" t="n">
+        <v>42.60305121511472</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.97874389217935</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.30293930023252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1870,72 +2043,81 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13.23</v>
+        <v>7914</v>
       </c>
       <c r="D20" t="n">
-        <v>1.66</v>
+        <v>24.06</v>
       </c>
       <c r="E20" t="n">
-        <v>3.05</v>
+        <v>13.04</v>
       </c>
       <c r="F20" t="n">
-        <v>0.44</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>3569</v>
+        <v>1.32</v>
       </c>
       <c r="H20" t="n">
-        <v>15.51</v>
+        <v>0.05</v>
       </c>
       <c r="I20" t="n">
-        <v>10.43</v>
+        <v>7906</v>
       </c>
       <c r="J20" t="n">
-        <v>5.92</v>
+        <v>19.07</v>
       </c>
       <c r="K20" t="n">
-        <v>65.54000000000001</v>
+        <v>23.25</v>
       </c>
       <c r="L20" t="n">
-        <v>11.1</v>
+        <v>20.11</v>
       </c>
       <c r="M20" t="n">
-        <v>1647269.48</v>
+        <v>5.73</v>
       </c>
       <c r="N20" t="n">
-        <v>14.5</v>
+        <v>2618348.58</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>9.81</v>
       </c>
       <c r="P20" t="n">
-        <v>0.49</v>
+        <v>3.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>61449</v>
+        <v>2.82</v>
       </c>
       <c r="R20" t="n">
-        <v>4280</v>
+        <v>26645</v>
       </c>
       <c r="S20" t="n">
-        <v>17</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>17</v>
+        <v>6412</v>
+      </c>
+      <c r="T20" t="n">
+        <v>100</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
       </c>
       <c r="V20" t="n">
-        <v>23.39827114613831</v>
+        <v>31</v>
+      </c>
+      <c r="W20" t="n">
+        <v>42.28401740380991</v>
+      </c>
+      <c r="X20" t="n">
+        <v>24.08396584592249</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19.10193873049559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1944,72 +2126,81 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13.56</v>
+        <v>78898</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03</v>
+        <v>5.71</v>
       </c>
       <c r="E21" t="n">
-        <v>73.29000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="G21" t="n">
-        <v>278</v>
+        <v>3.31</v>
       </c>
       <c r="H21" t="n">
-        <v>20.48</v>
+        <v>0.34</v>
       </c>
       <c r="I21" t="n">
-        <v>22.97</v>
+        <v>27809</v>
       </c>
       <c r="J21" t="n">
-        <v>22.74</v>
+        <v>13.17</v>
       </c>
       <c r="K21" t="n">
-        <v>64.79000000000001</v>
+        <v>38.36</v>
       </c>
       <c r="L21" t="n">
-        <v>19.4</v>
+        <v>67.03</v>
       </c>
       <c r="M21" t="n">
-        <v>3053088.97</v>
+        <v>13.1</v>
       </c>
       <c r="N21" t="n">
-        <v>72.53</v>
+        <v>378605.83</v>
       </c>
       <c r="O21" t="n">
-        <v>11.71</v>
+        <v>63.78</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>6.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>50789</v>
+        <v>1.02</v>
       </c>
       <c r="R21" t="n">
-        <v>2536</v>
+        <v>149982</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
+        <v>8558</v>
+      </c>
+      <c r="T21" t="n">
+        <v>52</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
       </c>
       <c r="V21" t="n">
-        <v>28.1325519519273</v>
+        <v>62</v>
+      </c>
+      <c r="W21" t="n">
+        <v>41.61679438329316</v>
+      </c>
+      <c r="X21" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.23276725060496</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2018,72 +2209,81 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.99</v>
+        <v>99263</v>
       </c>
       <c r="D22" t="n">
-        <v>6.45</v>
+        <v>9.66</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3</v>
+        <v>16.94</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="G22" t="n">
-        <v>12547</v>
+        <v>11.36</v>
       </c>
       <c r="H22" t="n">
-        <v>17.25</v>
+        <v>0.83</v>
       </c>
       <c r="I22" t="n">
-        <v>51.95</v>
+        <v>42060</v>
       </c>
       <c r="J22" t="n">
-        <v>55.18</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>63.6</v>
+        <v>10.97</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="M22" t="n">
-        <v>1319221.86</v>
+        <v>19.71</v>
       </c>
       <c r="N22" t="n">
-        <v>25.76</v>
+        <v>390111.05</v>
       </c>
       <c r="O22" t="n">
-        <v>6.2</v>
+        <v>18.15</v>
       </c>
       <c r="P22" t="n">
-        <v>3.43</v>
+        <v>10.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>159516</v>
+        <v>1.11</v>
       </c>
       <c r="R22" t="n">
-        <v>46081</v>
+        <v>591396</v>
       </c>
       <c r="S22" t="n">
-        <v>-14152</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>16</v>
+        <v>57101</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V22" t="n">
-        <v>21.39660074377121</v>
+        <v>31</v>
+      </c>
+      <c r="W22" t="n">
+        <v>40.25914787843672</v>
+      </c>
+      <c r="X22" t="n">
+        <v>27.42081401425274</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>24.85526395727469</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2092,68 +2292,81 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.46</v>
+        <v>24056</v>
       </c>
       <c r="D23" t="n">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="E23" t="n">
-        <v>6.53</v>
+        <v>9.57</v>
       </c>
       <c r="F23" t="n">
-        <v>1.19</v>
+        <v>0.53</v>
       </c>
       <c r="G23" t="n">
-        <v>45133</v>
+        <v>126.47</v>
       </c>
       <c r="H23" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9789</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10.59</v>
+      </c>
       <c r="K23" t="n">
-        <v>62.94</v>
+        <v>13.07</v>
       </c>
       <c r="L23" t="n">
-        <v>20.1</v>
+        <v>13.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1504106.64</v>
+        <v>11.3</v>
       </c>
       <c r="N23" t="n">
-        <v>67.06999999999999</v>
+        <v>722281.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.93</v>
+        <v>56.45</v>
       </c>
       <c r="P23" t="n">
-        <v>3.65</v>
+        <v>9.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>437928</v>
+        <v>0.98</v>
       </c>
       <c r="R23" t="n">
-        <v>31807</v>
+        <v>215962</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>7</v>
+        <v>10155</v>
+      </c>
+      <c r="T23" t="n">
+        <v>23872</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V23" t="n">
-        <v>20.57936456937097</v>
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>38.75359527497578</v>
+      </c>
+      <c r="X23" t="n">
+        <v>28.91520783117428</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.83085522343517</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,72 +2375,81 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10.36</v>
+        <v>12596</v>
       </c>
       <c r="D24" t="n">
-        <v>2.61</v>
+        <v>6.97</v>
       </c>
       <c r="E24" t="n">
-        <v>3.31</v>
+        <v>13.23</v>
       </c>
       <c r="F24" t="n">
-        <v>0.34</v>
+        <v>1.66</v>
       </c>
       <c r="G24" t="n">
-        <v>27809</v>
+        <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>13.17</v>
+        <v>0.44</v>
       </c>
       <c r="I24" t="n">
-        <v>38.36</v>
+        <v>3569</v>
       </c>
       <c r="J24" t="n">
-        <v>67.03</v>
+        <v>15.51</v>
       </c>
       <c r="K24" t="n">
-        <v>60.91</v>
+        <v>10.43</v>
       </c>
       <c r="L24" t="n">
-        <v>13.1</v>
+        <v>5.92</v>
       </c>
       <c r="M24" t="n">
-        <v>378605.83</v>
+        <v>11.1</v>
       </c>
       <c r="N24" t="n">
-        <v>63.78</v>
+        <v>1647269.48</v>
       </c>
       <c r="O24" t="n">
-        <v>6.28</v>
+        <v>14.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.02</v>
+        <v>3.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>149982</v>
+        <v>0.49</v>
       </c>
       <c r="R24" t="n">
-        <v>8558</v>
+        <v>61449</v>
       </c>
       <c r="S24" t="n">
-        <v>52</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>62</v>
+        <v>4280</v>
+      </c>
+      <c r="T24" t="n">
+        <v>17</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V24" t="n">
-        <v>14.23276725060496</v>
+        <v>17</v>
+      </c>
+      <c r="W24" t="n">
+        <v>38.44284345266653</v>
+      </c>
+      <c r="X24" t="n">
+        <v>22.27556511123987</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>23.39827114613831</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2236,72 +2458,81 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16.72</v>
+        <v>3347</v>
       </c>
       <c r="D25" t="n">
-        <v>14.87</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.61</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G25" t="n">
-        <v>13296</v>
+        <v>19.83</v>
       </c>
       <c r="H25" t="n">
-        <v>18.18</v>
+        <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>85.78</v>
+        <v>1929</v>
       </c>
       <c r="J25" t="n">
-        <v>53.42</v>
+        <v>10.33</v>
       </c>
       <c r="K25" t="n">
-        <v>59.34</v>
+        <v>11.29</v>
       </c>
       <c r="L25" t="n">
-        <v>6.63</v>
+        <v>10.68</v>
       </c>
       <c r="M25" t="n">
-        <v>496415.88</v>
+        <v>14.8</v>
       </c>
       <c r="N25" t="n">
-        <v>36.74</v>
+        <v>3154358.33</v>
       </c>
       <c r="O25" t="n">
-        <v>12.61</v>
+        <v>25.87</v>
       </c>
       <c r="P25" t="n">
-        <v>3.81</v>
+        <v>1.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>110519</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>15401</v>
+        <v>20521</v>
       </c>
       <c r="S25" t="n">
-        <v>-7745</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>19</v>
+        <v>1733</v>
+      </c>
+      <c r="T25" t="n">
+        <v>22</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
       </c>
       <c r="V25" t="n">
-        <v>16.30293930023252</v>
+        <v>16</v>
+      </c>
+      <c r="W25" t="n">
+        <v>38.11747535171825</v>
+      </c>
+      <c r="X25" t="n">
+        <v>27.25430316031267</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.80997180241832</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2310,72 +2541,81 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13.04</v>
+        <v>40785</v>
       </c>
       <c r="D26" t="n">
-        <v>8.380000000000001</v>
+        <v>11.95</v>
       </c>
       <c r="E26" t="n">
-        <v>1.32</v>
+        <v>13.27</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05</v>
+        <v>1.48</v>
       </c>
       <c r="G26" t="n">
-        <v>7906</v>
+        <v>4.6</v>
       </c>
       <c r="H26" t="n">
-        <v>19.07</v>
+        <v>0.37</v>
       </c>
       <c r="I26" t="n">
-        <v>23.25</v>
+        <v>8644</v>
       </c>
       <c r="J26" t="n">
-        <v>20.11</v>
+        <v>12.22</v>
       </c>
       <c r="K26" t="n">
-        <v>49.7</v>
+        <v>8.74</v>
       </c>
       <c r="L26" t="n">
-        <v>5.73</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>2618348.58</v>
+        <v>10.58</v>
       </c>
       <c r="N26" t="n">
-        <v>9.81</v>
+        <v>907823.11</v>
       </c>
       <c r="O26" t="n">
-        <v>3.91</v>
+        <v>30.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>5.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>26645</v>
+        <v>0.06</v>
       </c>
       <c r="R26" t="n">
-        <v>6412</v>
+        <v>178501</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U26" t="n">
-        <v>31</v>
+        <v>21332</v>
+      </c>
+      <c r="T26" t="n">
+        <v>29</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V26" t="n">
-        <v>19.10193873049559</v>
+        <v>36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>38.05733944263428</v>
+      </c>
+      <c r="X26" t="n">
+        <v>21.18350474042158</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>16.97193810203161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2384,66 +2624,75 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14.34</v>
+        <v>158788</v>
       </c>
       <c r="D27" t="n">
-        <v>6.81</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="G27" t="n">
-        <v>35669</v>
+        <v>7.73</v>
       </c>
       <c r="H27" t="n">
-        <v>21.95</v>
+        <v>0.51</v>
       </c>
       <c r="I27" t="n">
-        <v>23.87</v>
+        <v>45207</v>
       </c>
       <c r="J27" t="n">
-        <v>15.42</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>49.05</v>
+        <v>14.68</v>
       </c>
       <c r="L27" t="n">
-        <v>7.67</v>
+        <v>11.95</v>
       </c>
       <c r="M27" t="n">
-        <v>808359.03</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>49.42</v>
+        <v>432472.71</v>
       </c>
       <c r="O27" t="n">
-        <v>4.4</v>
+        <v>58.34</v>
       </c>
       <c r="P27" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>283649</v>
+        <v>4.21</v>
       </c>
       <c r="R27" t="n">
-        <v>65446</v>
+        <v>899041</v>
       </c>
       <c r="S27" t="n">
-        <v>-44685</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>23</v>
+        <v>79020</v>
+      </c>
+      <c r="T27" t="n">
+        <v>18</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
       </c>
       <c r="V27" t="n">
-        <v>30.18695614094877</v>
+        <v>10</v>
+      </c>
+      <c r="W27" t="n">
+        <v>36.68282246218183</v>
+      </c>
+      <c r="X27" t="n">
+        <v>17.28975659693698</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>24.46173600944801</v>
       </c>
     </row>
   </sheetData>
